--- a/assets/templates/csv excel format/ICT_BSCS_Test.xlsx
+++ b/assets/templates/csv excel format/ICT_BSCS_Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\OnlineClearanceWebsite\assets\templates\csv excel format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A218797E-9FB8-4E8E-A0D0-B8373E17BD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABBB024-B866-46B3-A6C6-8B43C699699B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9420" xr2:uid="{7D73B4CE-2E72-49DB-9985-22AC5D9E7A3C}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9420" xr2:uid="{7D73B4CE-2E72-49DB-9985-22AC5D9E7A3C}"/>
   </bookViews>
   <sheets>
     <sheet name="ICT_BSCS_Test" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
   <si>
     <t>Student Number</t>
   </si>
@@ -64,9 +64,6 @@
     <t>BS in Computer Science</t>
   </si>
   <si>
-    <t>3rd Year</t>
-  </si>
-  <si>
     <t>xyz</t>
   </si>
   <si>
@@ -79,9 +76,6 @@
     <t>dsa</t>
   </si>
   <si>
-    <t>2nd year</t>
-  </si>
-  <si>
     <t>vbn</t>
   </si>
   <si>
@@ -110,6 +104,9 @@
   </si>
   <si>
     <t>02000250002</t>
+  </si>
+  <si>
+    <t>1st Year</t>
   </si>
 </sst>
 </file>
@@ -988,7 +985,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1009,7 +1006,7 @@
         <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -1017,7 +1014,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -1026,10 +1023,10 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1038,7 +1035,7 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1046,7 +1043,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -1055,10 +1052,10 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -1067,7 +1064,7 @@
         <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4">
         <v>3</v>
@@ -1075,7 +1072,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -1084,10 +1081,10 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -1096,7 +1093,7 @@
         <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I5">
         <v>4</v>
@@ -1104,7 +1101,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -1113,10 +1110,10 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -1125,7 +1122,7 @@
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I6">
         <v>1</v>
